--- a/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D5D2A4-6771-4C06-94FC-AFA349F2B049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B25899-8B38-4472-B86C-56C5A07DA1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="AFSA" sheetId="15" r:id="rId1"/>
@@ -685,10 +685,10 @@
     <t>Table 16.7 Gross Value Added in Accommodation and Food Service Activities, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -737,10 +737,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1206,7 +1208,7 @@
     </row>
     <row r="3" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:233" x14ac:dyDescent="0.2">
@@ -1216,7 +1218,7 @@
     </row>
     <row r="6" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:233" x14ac:dyDescent="0.2">
@@ -2002,22 +2004,22 @@
         <v>35475.744175264444</v>
       </c>
       <c r="CV12" s="19">
-        <v>34700.442165620261</v>
+        <v>34709.566638872006</v>
       </c>
       <c r="CW12" s="19">
-        <v>48204.599693784949</v>
+        <v>49083.796465493673</v>
       </c>
       <c r="CX12" s="19">
-        <v>50743.051809200879</v>
+        <v>50704.126969777586</v>
       </c>
       <c r="CY12" s="19">
-        <v>37387.302762702791</v>
+        <v>37343.467584743063</v>
       </c>
       <c r="CZ12" s="19">
-        <v>36770.558515900426</v>
+        <v>36737.17355971341</v>
       </c>
       <c r="DA12" s="19">
-        <v>51382.78996416297</v>
+        <v>52197.206566962675</v>
       </c>
       <c r="DB12" s="8"/>
       <c r="DC12" s="8"/>
@@ -2444,25 +2446,25 @@
         <v>117928.35605530016</v>
       </c>
       <c r="CU13" s="19">
-        <v>89666.188722286111</v>
+        <v>89698.842397155473</v>
       </c>
       <c r="CV13" s="19">
-        <v>98457.073338885879</v>
+        <v>98476.657118372881</v>
       </c>
       <c r="CW13" s="19">
-        <v>115242.51524806008</v>
+        <v>115727.64409136909</v>
       </c>
       <c r="CX13" s="19">
-        <v>127432.66614043809</v>
+        <v>127327.45616577915</v>
       </c>
       <c r="CY13" s="19">
-        <v>98983.277586466167</v>
+        <v>99101.754723019898</v>
       </c>
       <c r="CZ13" s="19">
-        <v>106010.78908207649</v>
+        <v>106038.06081885257</v>
       </c>
       <c r="DA13" s="19">
-        <v>126025.84268366828</v>
+        <v>126616.67630623671</v>
       </c>
       <c r="DB13" s="8"/>
       <c r="DC13" s="8"/>
@@ -3123,25 +3125,25 @@
         <v>164210.33434738737</v>
       </c>
       <c r="CU15" s="20">
-        <v>125141.93289755055</v>
+        <v>125174.58657241991</v>
       </c>
       <c r="CV15" s="20">
-        <v>133157.51550450613</v>
+        <v>133186.22375724488</v>
       </c>
       <c r="CW15" s="20">
-        <v>163447.11494184504</v>
+        <v>164811.44055686277</v>
       </c>
       <c r="CX15" s="20">
-        <v>178175.71794963896</v>
+        <v>178031.58313555672</v>
       </c>
       <c r="CY15" s="20">
-        <v>136370.58034916897</v>
+        <v>136445.22230776295</v>
       </c>
       <c r="CZ15" s="20">
-        <v>142781.34759797691</v>
+        <v>142775.23437856598</v>
       </c>
       <c r="DA15" s="20">
-        <v>177408.63264783125</v>
+        <v>178813.88287319939</v>
       </c>
       <c r="DB15" s="8"/>
       <c r="DC15" s="8"/>
@@ -3864,7 +3866,7 @@
     </row>
     <row r="22" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:233" x14ac:dyDescent="0.2">
@@ -3874,7 +3876,7 @@
     </row>
     <row r="25" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:233" x14ac:dyDescent="0.2">
@@ -4660,22 +4662,22 @@
         <v>29608.426750846269</v>
       </c>
       <c r="CV31" s="19">
-        <v>29785.332130576724</v>
+        <v>29793.164176780127</v>
       </c>
       <c r="CW31" s="19">
-        <v>40724.151013428396</v>
+        <v>41466.912955837004</v>
       </c>
       <c r="CX31" s="19">
-        <v>41214.441983885736</v>
+        <v>41182.82651183696</v>
       </c>
       <c r="CY31" s="19">
-        <v>30791.67092826571</v>
+        <v>30755.568875561221</v>
       </c>
       <c r="CZ31" s="19">
-        <v>30912.72554145367</v>
+        <v>30884.659065732991</v>
       </c>
       <c r="DA31" s="19">
-        <v>42457.627308138399</v>
+        <v>43130.580190209352</v>
       </c>
       <c r="DB31" s="8"/>
       <c r="DC31" s="8"/>
@@ -5102,25 +5104,25 @@
         <v>83537.671086025191</v>
       </c>
       <c r="CU32" s="19">
-        <v>65713.034534559905</v>
+        <v>65736.965205584856</v>
       </c>
       <c r="CV32" s="19">
-        <v>73886.132256004785</v>
+        <v>73900.828708704241</v>
       </c>
       <c r="CW32" s="19">
-        <v>85380.228177188546</v>
+        <v>85739.647713007435</v>
       </c>
       <c r="CX32" s="19">
-        <v>87779.412343530683</v>
+        <v>87706.097774052178</v>
       </c>
       <c r="CY32" s="19">
-        <v>71011.090888279272</v>
+        <v>71096.086969608747</v>
       </c>
       <c r="CZ32" s="19">
-        <v>77746.224127872425</v>
+        <v>77766.224682326458</v>
       </c>
       <c r="DA32" s="19">
-        <v>91046.23245335609</v>
+        <v>91473.074870721612</v>
       </c>
       <c r="DB32" s="8"/>
       <c r="DC32" s="8"/>
@@ -5781,25 +5783,25 @@
         <v>121566.35090343711</v>
       </c>
       <c r="CU34" s="20">
-        <v>95321.461285406171</v>
+        <v>95345.391956431122</v>
       </c>
       <c r="CV34" s="20">
-        <v>103671.4643865815</v>
+        <v>103693.99288548436</v>
       </c>
       <c r="CW34" s="20">
-        <v>126104.37919061695</v>
+        <v>127206.56066884444</v>
       </c>
       <c r="CX34" s="20">
-        <v>128993.85432741643</v>
+        <v>128888.92428588914</v>
       </c>
       <c r="CY34" s="20">
-        <v>101802.76181654498</v>
+        <v>101851.65584516997</v>
       </c>
       <c r="CZ34" s="20">
-        <v>108658.9496693261</v>
+        <v>108650.88374805945</v>
       </c>
       <c r="DA34" s="20">
-        <v>133503.8597614945</v>
+        <v>134603.65506093096</v>
       </c>
       <c r="DB34" s="8"/>
       <c r="DC34" s="8"/>
@@ -6530,7 +6532,7 @@
     </row>
     <row r="41" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
@@ -6554,7 +6556,7 @@
     </row>
     <row r="44" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX44" s="4"/>
       <c r="CY44" s="4"/>
@@ -7336,22 +7338,22 @@
         <v>18.509069354893896</v>
       </c>
       <c r="CR50" s="16">
-        <v>14.62656470324329</v>
+        <v>14.656705731953593</v>
       </c>
       <c r="CS50" s="16">
-        <v>11.989564438331456</v>
+        <v>14.032126022593332</v>
       </c>
       <c r="CT50" s="16">
-        <v>9.6388998088190192</v>
+        <v>9.5547961450178889</v>
       </c>
       <c r="CU50" s="16">
-        <v>5.3883537382457121</v>
+        <v>5.2647899371788043</v>
       </c>
       <c r="CV50" s="16">
-        <v>5.9656771530454762</v>
+        <v>5.8416370965883573</v>
       </c>
       <c r="CW50" s="16">
-        <v>6.5931265700102557</v>
+        <v>6.3430507125864892</v>
       </c>
       <c r="CX50" s="18"/>
       <c r="CY50" s="18"/>
@@ -7766,25 +7768,25 @@
         <v>18.038849943608199</v>
       </c>
       <c r="CQ51" s="16">
-        <v>16.626969096450409</v>
+        <v>16.669441060343829</v>
       </c>
       <c r="CR51" s="16">
-        <v>15.113266274639543</v>
+        <v>15.136163083840756</v>
       </c>
       <c r="CS51" s="16">
-        <v>8.7850853524816159</v>
+        <v>9.2430307775074709</v>
       </c>
       <c r="CT51" s="16">
-        <v>8.059393349535938</v>
+        <v>7.9701781868912462</v>
       </c>
       <c r="CU51" s="16">
-        <v>10.390860810463252</v>
+        <v>10.482757719694519</v>
       </c>
       <c r="CV51" s="16">
-        <v>7.6720904725564765</v>
+        <v>7.6783716281012317</v>
       </c>
       <c r="CW51" s="16">
-        <v>9.3570740038058346</v>
+        <v>9.4091885308496614</v>
       </c>
       <c r="CX51" s="18"/>
       <c r="CY51" s="18"/>
@@ -8430,25 +8432,25 @@
         <v>18.470642360646366</v>
       </c>
       <c r="CQ53" s="16">
-        <v>17.154415681399442</v>
+        <v>17.184985148488494</v>
       </c>
       <c r="CR53" s="16">
-        <v>14.986035580174146</v>
+        <v>15.010826131111926</v>
       </c>
       <c r="CS53" s="16">
-        <v>9.7109362002686339</v>
+        <v>10.626715231050923</v>
       </c>
       <c r="CT53" s="16">
-        <v>8.5045704691811892</v>
+        <v>8.4167959605578062</v>
       </c>
       <c r="CU53" s="16">
-        <v>8.9727297570279205</v>
+        <v>9.0039328620609353</v>
       </c>
       <c r="CV53" s="16">
-        <v>7.2274043691849386</v>
+        <v>7.1997015538174196</v>
       </c>
       <c r="CW53" s="16">
-        <v>8.5419174948140153</v>
+        <v>8.4960378169290465</v>
       </c>
       <c r="CX53" s="18"/>
       <c r="CY53" s="18"/>
@@ -9175,7 +9177,7 @@
     </row>
     <row r="60" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX60" s="4"/>
       <c r="CY60" s="4"/>
@@ -9199,7 +9201,7 @@
     </row>
     <row r="63" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
@@ -9981,22 +9983,22 @@
         <v>15.491331771401079</v>
       </c>
       <c r="CR69" s="16">
-        <v>12.162387896985621</v>
+        <v>12.191880970973926</v>
       </c>
       <c r="CS69" s="16">
-        <v>9.8694724290537863</v>
+        <v>11.873365959600406</v>
       </c>
       <c r="CT69" s="16">
-        <v>8.3772620605545569</v>
+        <v>8.2941261952009171</v>
       </c>
       <c r="CU69" s="16">
-        <v>3.9963088460470857</v>
+        <v>3.8743771642043185</v>
       </c>
       <c r="CV69" s="16">
-        <v>3.7850624123798156</v>
+        <v>3.6635749142870111</v>
       </c>
       <c r="CW69" s="16">
-        <v>4.2566296695501649</v>
+        <v>4.0120354175971187</v>
       </c>
       <c r="CX69" s="18"/>
       <c r="CY69" s="18"/>
@@ -10411,25 +10413,25 @@
         <v>11.802952856935462</v>
       </c>
       <c r="CQ70" s="16">
-        <v>10.753232854313509</v>
+        <v>10.79356578368072</v>
       </c>
       <c r="CR70" s="16">
-        <v>10.055304200023627</v>
+        <v>10.077194946272144</v>
       </c>
       <c r="CS70" s="16">
-        <v>4.7477007414617134</v>
+        <v>5.1886502538061876</v>
       </c>
       <c r="CT70" s="16">
-        <v>5.0776388692203938</v>
+        <v>4.9898765836246923</v>
       </c>
       <c r="CU70" s="16">
-        <v>8.0624131745628063</v>
+        <v>8.1523717245903384</v>
       </c>
       <c r="CV70" s="16">
-        <v>5.2243793984140012</v>
+        <v>5.230517764365672</v>
       </c>
       <c r="CW70" s="16">
-        <v>6.6362018433693493</v>
+        <v>6.6870197284988109</v>
       </c>
       <c r="CX70" s="18"/>
       <c r="CY70" s="18"/>
@@ -11074,25 +11076,25 @@
         <v>13.151748004563999</v>
       </c>
       <c r="CQ72" s="16">
-        <v>12.182803637154365</v>
+        <v>12.210967386768502</v>
       </c>
       <c r="CR72" s="16">
-        <v>10.652530748919162</v>
+        <v>10.676576279985255</v>
       </c>
       <c r="CS72" s="16">
-        <v>6.348722836485976</v>
+        <v>7.2782353030303995</v>
       </c>
       <c r="CT72" s="16">
-        <v>6.1098349738893916</v>
+        <v>6.0235199362597598</v>
       </c>
       <c r="CU72" s="16">
-        <v>6.799413735100913</v>
+        <v>6.8238891835611213</v>
       </c>
       <c r="CV72" s="16">
-        <v>4.8108564032111332</v>
+        <v>4.7803066741284539</v>
       </c>
       <c r="CW72" s="16">
-        <v>5.8677427527656647</v>
+        <v>5.8150258549504343</v>
       </c>
       <c r="CX72" s="18"/>
       <c r="CY72" s="18"/>
@@ -11818,7 +11820,7 @@
     </row>
     <row r="78" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
@@ -11842,7 +11844,7 @@
     </row>
     <row r="81" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:233" x14ac:dyDescent="0.2">
@@ -12628,19 +12630,19 @@
         <v>119.81637685038594</v>
       </c>
       <c r="CV87" s="16">
-        <v>116.50178018326622</v>
+        <v>116.50178018326625</v>
       </c>
       <c r="CW87" s="16">
-        <v>118.36858103656955</v>
+        <v>118.36858103656954</v>
       </c>
       <c r="CX87" s="16">
         <v>123.11958955805029</v>
       </c>
       <c r="CY87" s="16">
-        <v>121.42018161275723</v>
+        <v>121.4201816127572</v>
       </c>
       <c r="CZ87" s="16">
-        <v>118.94958426293229</v>
+        <v>118.94958426293225</v>
       </c>
       <c r="DA87" s="16">
         <v>121.02134109202511</v>
@@ -13070,22 +13072,22 @@
         <v>141.1678761475888</v>
       </c>
       <c r="CU88" s="16">
-        <v>136.4511460433755</v>
+        <v>136.45114604337542</v>
       </c>
       <c r="CV88" s="16">
-        <v>133.25514590173205</v>
+        <v>133.25514590173199</v>
       </c>
       <c r="CW88" s="16">
         <v>134.975646831136</v>
       </c>
       <c r="CX88" s="16">
-        <v>145.17375172406227</v>
+        <v>145.17514676550681</v>
       </c>
       <c r="CY88" s="16">
-        <v>139.39129275199437</v>
+        <v>139.39129275199446</v>
       </c>
       <c r="CZ88" s="16">
-        <v>136.35490375418897</v>
+        <v>136.35490375418894</v>
       </c>
       <c r="DA88" s="16">
         <v>138.41961307760056</v>
@@ -13749,25 +13751,25 @@
         <v>135.07877231407838</v>
       </c>
       <c r="CU90" s="16">
-        <v>131.28411084976719</v>
+        <v>131.28540772019636</v>
       </c>
       <c r="CV90" s="16">
-        <v>128.44181983190072</v>
+        <v>128.44160018442977</v>
       </c>
       <c r="CW90" s="16">
-        <v>129.61256063501295</v>
+        <v>129.56206007795049</v>
       </c>
       <c r="CX90" s="16">
-        <v>138.12729209361208</v>
+        <v>138.12791449842814</v>
       </c>
       <c r="CY90" s="16">
-        <v>133.95567852561544</v>
+        <v>133.96465788949027</v>
       </c>
       <c r="CZ90" s="16">
-        <v>131.40320979771388</v>
+        <v>131.40733830535086</v>
       </c>
       <c r="DA90" s="16">
-        <v>132.88651950945308</v>
+        <v>132.84474540624905</v>
       </c>
       <c r="DB90" s="8"/>
       <c r="DC90" s="8"/>
@@ -14022,7 +14024,7 @@
     </row>
     <row r="97" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:233" x14ac:dyDescent="0.2">
@@ -14032,7 +14034,7 @@
     </row>
     <row r="100" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:233" x14ac:dyDescent="0.2">
@@ -14815,25 +14817,25 @@
         <v>28.184571011333297</v>
       </c>
       <c r="CU106" s="16">
-        <v>28.348406768103246</v>
+        <v>28.341011659535148</v>
       </c>
       <c r="CV106" s="16">
-        <v>26.059694816434131</v>
+        <v>26.060928570312381</v>
       </c>
       <c r="CW106" s="16">
-        <v>29.492475110947225</v>
+        <v>29.781789601286157</v>
       </c>
       <c r="CX106" s="16">
-        <v>28.479218376739368</v>
+        <v>28.48041121511034</v>
       </c>
       <c r="CY106" s="16">
-        <v>27.415959268468882</v>
+        <v>27.368834872438352</v>
       </c>
       <c r="CZ106" s="16">
-        <v>25.753054677305364</v>
+        <v>25.730774471926587</v>
       </c>
       <c r="DA106" s="16">
-        <v>28.962959241200771</v>
+        <v>29.190802038551332</v>
       </c>
       <c r="DB106" s="8"/>
       <c r="DC106" s="8"/>
@@ -15260,25 +15262,25 @@
         <v>71.81542898866671</v>
       </c>
       <c r="CU107" s="16">
-        <v>71.651593231896754</v>
+        <v>71.658988340464859</v>
       </c>
       <c r="CV107" s="16">
-        <v>73.940305183565883</v>
+        <v>73.93907142968763</v>
       </c>
       <c r="CW107" s="16">
-        <v>70.507524889052775</v>
+        <v>70.218210398713836</v>
       </c>
       <c r="CX107" s="16">
-        <v>71.520781623260646</v>
+        <v>71.519588784889663</v>
       </c>
       <c r="CY107" s="16">
-        <v>72.584040731531104</v>
+        <v>72.631165127561658</v>
       </c>
       <c r="CZ107" s="16">
-        <v>74.246945322694629</v>
+        <v>74.269225528073406</v>
       </c>
       <c r="DA107" s="16">
-        <v>71.037040758799236</v>
+        <v>70.80919796144866</v>
       </c>
       <c r="DB107" s="8"/>
       <c r="DC107" s="8"/>
@@ -16680,7 +16682,7 @@
     </row>
     <row r="116" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:233" x14ac:dyDescent="0.2">
@@ -16690,7 +16692,7 @@
     </row>
     <row r="119" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120" spans="1:233" x14ac:dyDescent="0.2">
@@ -17473,25 +17475,25 @@
         <v>31.282241783846054</v>
       </c>
       <c r="CU125" s="16">
-        <v>31.061658467650194</v>
+        <v>31.053862324438384</v>
       </c>
       <c r="CV125" s="16">
-        <v>28.730501982213656</v>
+        <v>28.731813046954947</v>
       </c>
       <c r="CW125" s="16">
-        <v>32.294002218488032</v>
+        <v>32.598093005428709</v>
       </c>
       <c r="CX125" s="16">
-        <v>31.950701991797136</v>
+        <v>31.952184208232769</v>
       </c>
       <c r="CY125" s="16">
-        <v>30.246400371489184</v>
+        <v>30.196434825089511</v>
       </c>
       <c r="CZ125" s="16">
-        <v>28.449313779976819</v>
+        <v>28.425593976159995</v>
       </c>
       <c r="DA125" s="16">
-        <v>31.802546670927136</v>
+        <v>32.042651568923183</v>
       </c>
       <c r="DB125" s="8"/>
       <c r="DC125" s="8"/>
@@ -17918,25 +17920,25 @@
         <v>68.717758216153939</v>
       </c>
       <c r="CU126" s="16">
-        <v>68.93834153234981</v>
+        <v>68.94613767556163</v>
       </c>
       <c r="CV126" s="16">
-        <v>71.269498017786347</v>
+        <v>71.26818695304506</v>
       </c>
       <c r="CW126" s="16">
-        <v>67.705997781511968</v>
+        <v>67.401906994571291</v>
       </c>
       <c r="CX126" s="16">
-        <v>68.049298008202868</v>
+        <v>68.047815791767235</v>
       </c>
       <c r="CY126" s="16">
-        <v>69.753599628510827</v>
+        <v>69.803565174910489</v>
       </c>
       <c r="CZ126" s="16">
-        <v>71.550686220023181</v>
+        <v>71.574406023839998</v>
       </c>
       <c r="DA126" s="16">
-        <v>68.197453329072857</v>
+        <v>67.957348431076809</v>
       </c>
       <c r="DB126" s="8"/>
       <c r="DC126" s="8"/>

--- a/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B25899-8B38-4472-B86C-56C5A07DA1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614E9163-9017-4D01-9899-D8EDB4BB8E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="AFSA" sheetId="15" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">AFSA!$A$1:$DA$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">AFSA!$A$1:$DB$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,10 +685,13 @@
     <t>Table 16.7 Gross Value Added in Accommodation and Food Service Activities, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1192,8 +1195,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.7109375" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="3" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="3"/>
+    <col min="2" max="106" width="13" style="3" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:233" x14ac:dyDescent="0.2">
@@ -1208,7 +1211,7 @@
     </row>
     <row r="3" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:233" x14ac:dyDescent="0.2">
@@ -1218,7 +1221,7 @@
     </row>
     <row r="6" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:233" x14ac:dyDescent="0.2">
@@ -1384,6 +1387,9 @@
       <c r="CY9" s="22"/>
       <c r="CZ9" s="22"/>
       <c r="DA9" s="22"/>
+      <c r="DB9" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1700,6 +1706,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2021,7 +2030,9 @@
       <c r="DA12" s="19">
         <v>52197.206566962675</v>
       </c>
-      <c r="DB12" s="8"/>
+      <c r="DB12" s="19">
+        <v>53445.042458122043</v>
+      </c>
       <c r="DC12" s="8"/>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
@@ -2466,7 +2477,9 @@
       <c r="DA13" s="19">
         <v>126616.67630623671</v>
       </c>
-      <c r="DB13" s="8"/>
+      <c r="DB13" s="19">
+        <v>139267.9258134824</v>
+      </c>
       <c r="DC13" s="8"/>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
@@ -3145,7 +3158,9 @@
       <c r="DA15" s="20">
         <v>178813.88287319939</v>
       </c>
-      <c r="DB15" s="8"/>
+      <c r="DB15" s="20">
+        <v>192712.96827160445</v>
+      </c>
       <c r="DC15" s="8"/>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
@@ -3380,6 +3395,7 @@
       <c r="CY16" s="10"/>
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
+      <c r="DB16" s="10"/>
     </row>
     <row r="17" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3725,7 +3741,7 @@
       <c r="CY19" s="21"/>
       <c r="CZ19" s="21"/>
       <c r="DA19" s="21"/>
-      <c r="DB19" s="8"/>
+      <c r="DB19" s="21"/>
       <c r="DC19" s="8"/>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
@@ -3866,7 +3882,7 @@
     </row>
     <row r="22" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:233" x14ac:dyDescent="0.2">
@@ -3876,7 +3892,7 @@
     </row>
     <row r="25" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:233" x14ac:dyDescent="0.2">
@@ -4042,6 +4058,9 @@
       <c r="CY28" s="22"/>
       <c r="CZ28" s="22"/>
       <c r="DA28" s="22"/>
+      <c r="DB28" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4358,6 +4377,9 @@
       </c>
       <c r="DA29" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB29" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4679,7 +4701,9 @@
       <c r="DA31" s="19">
         <v>43130.580190209352</v>
       </c>
-      <c r="DB31" s="8"/>
+      <c r="DB31" s="19">
+        <v>42207.64831855493</v>
+      </c>
       <c r="DC31" s="8"/>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
@@ -5124,7 +5148,9 @@
       <c r="DA32" s="19">
         <v>91473.074870721612</v>
       </c>
-      <c r="DB32" s="8"/>
+      <c r="DB32" s="19">
+        <v>91822.325463675021</v>
+      </c>
       <c r="DC32" s="8"/>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
@@ -5803,7 +5829,9 @@
       <c r="DA34" s="20">
         <v>134603.65506093096</v>
       </c>
-      <c r="DB34" s="8"/>
+      <c r="DB34" s="20">
+        <v>134029.97378222994</v>
+      </c>
       <c r="DC34" s="8"/>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
@@ -6038,6 +6066,7 @@
       <c r="CY35" s="10"/>
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
+      <c r="DB35" s="10"/>
     </row>
     <row r="36" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6149,7 +6178,7 @@
       <c r="CY37" s="7"/>
       <c r="CZ37" s="7"/>
       <c r="DA37" s="7"/>
-      <c r="DB37" s="8"/>
+      <c r="DB37" s="7"/>
       <c r="DC37" s="8"/>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
@@ -6383,7 +6412,7 @@
       <c r="CY38" s="7"/>
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
-      <c r="DB38" s="8"/>
+      <c r="DB38" s="7"/>
       <c r="DC38" s="8"/>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
@@ -6520,6 +6549,7 @@
       <c r="CY39" s="4"/>
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
+      <c r="DB39" s="4"/>
     </row>
     <row r="40" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -6529,21 +6559,24 @@
       <c r="CY40" s="4"/>
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
+      <c r="DB40" s="4"/>
     </row>
     <row r="41" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
+      <c r="DB41" s="4"/>
     </row>
     <row r="42" spans="1:233" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
       <c r="CY42" s="4"/>
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
+      <c r="DB42" s="4"/>
     </row>
     <row r="43" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -6553,15 +6586,17 @@
       <c r="CY43" s="4"/>
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
+      <c r="DB43" s="4"/>
     </row>
     <row r="44" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX44" s="4"/>
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
+      <c r="DB44" s="4"/>
     </row>
     <row r="45" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6571,12 +6606,14 @@
       <c r="CY45" s="4"/>
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
+      <c r="DB45" s="4"/>
     </row>
     <row r="46" spans="1:233" x14ac:dyDescent="0.2">
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
+      <c r="DB46" s="4"/>
     </row>
     <row r="47" spans="1:233" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
@@ -6730,10 +6767,13 @@
       <c r="CU47" s="22"/>
       <c r="CV47" s="22"/>
       <c r="CW47" s="22"/>
-      <c r="CX47" s="23"/>
+      <c r="CX47" s="22" t="s">
+        <v>53</v>
+      </c>
       <c r="CY47" s="23"/>
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
+      <c r="DB47" s="23"/>
     </row>
     <row r="48" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -7039,17 +7079,20 @@
       <c r="CW48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX48" s="24"/>
+      <c r="CX48" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY48" s="24"/>
       <c r="CZ48" s="24"/>
       <c r="DA48" s="24"/>
+      <c r="DB48" s="24"/>
     </row>
     <row r="49" spans="1:229" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
+      <c r="DB49" s="4"/>
     </row>
     <row r="50" spans="1:229" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -7355,11 +7398,13 @@
       <c r="CW50" s="16">
         <v>6.3430507125864892</v>
       </c>
-      <c r="CX50" s="18"/>
+      <c r="CX50" s="16">
+        <v>5.4057049241340565</v>
+      </c>
       <c r="CY50" s="18"/>
       <c r="CZ50" s="18"/>
       <c r="DA50" s="18"/>
-      <c r="DB50" s="8"/>
+      <c r="DB50" s="18"/>
       <c r="DC50" s="8"/>
       <c r="DD50" s="8"/>
       <c r="DE50" s="8"/>
@@ -7788,11 +7833,13 @@
       <c r="CW51" s="16">
         <v>9.4091885308496614</v>
       </c>
-      <c r="CX51" s="18"/>
+      <c r="CX51" s="16">
+        <v>9.3777650219893474</v>
+      </c>
       <c r="CY51" s="18"/>
       <c r="CZ51" s="18"/>
       <c r="DA51" s="18"/>
-      <c r="DB51" s="8"/>
+      <c r="DB51" s="18"/>
       <c r="DC51" s="8"/>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
@@ -8019,11 +8066,11 @@
       <c r="CU52" s="8"/>
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
-      <c r="CX52" s="7"/>
+      <c r="CX52" s="8"/>
       <c r="CY52" s="7"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
-      <c r="DB52" s="8"/>
+      <c r="DB52" s="7"/>
       <c r="DC52" s="8"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
@@ -8452,11 +8499,13 @@
       <c r="CW53" s="16">
         <v>8.4960378169290465</v>
       </c>
-      <c r="CX53" s="18"/>
+      <c r="CX53" s="16">
+        <v>8.2465059724088547</v>
+      </c>
       <c r="CY53" s="18"/>
       <c r="CZ53" s="18"/>
       <c r="DA53" s="18"/>
-      <c r="DB53" s="8"/>
+      <c r="DB53" s="18"/>
       <c r="DC53" s="8"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
@@ -8683,19 +8732,20 @@
       <c r="CU54" s="10"/>
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
-      <c r="CX54" s="25"/>
+      <c r="CX54" s="10"/>
       <c r="CY54" s="25"/>
       <c r="CZ54" s="25"/>
       <c r="DA54" s="25"/>
+      <c r="DB54" s="25"/>
     </row>
     <row r="55" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX55" s="4"/>
       <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
+      <c r="DB55" s="4"/>
     </row>
     <row r="56" spans="1:229" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -8798,11 +8848,11 @@
       <c r="CU56" s="8"/>
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
-      <c r="CX56" s="7"/>
+      <c r="CX56" s="8"/>
       <c r="CY56" s="7"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
-      <c r="DB56" s="8"/>
+      <c r="DB56" s="7"/>
       <c r="DC56" s="8"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
@@ -9028,11 +9078,11 @@
       <c r="CU57" s="8"/>
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
-      <c r="CX57" s="7"/>
+      <c r="CX57" s="8"/>
       <c r="CY57" s="7"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
-      <c r="DB57" s="8"/>
+      <c r="DB57" s="7"/>
       <c r="DC57" s="8"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
@@ -9161,67 +9211,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX58" s="4"/>
       <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
+      <c r="DB58" s="4"/>
     </row>
     <row r="59" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX59" s="4"/>
       <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
+      <c r="DB59" s="4"/>
     </row>
     <row r="60" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CX60" s="4"/>
+        <v>51</v>
+      </c>
       <c r="CY60" s="4"/>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
+      <c r="DB60" s="4"/>
     </row>
     <row r="61" spans="1:229" x14ac:dyDescent="0.2">
-      <c r="CX61" s="4"/>
       <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
+      <c r="DB61" s="4"/>
     </row>
     <row r="62" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CX62" s="4"/>
       <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
+      <c r="DB62" s="4"/>
     </row>
     <row r="63" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="CX63" s="4"/>
+        <v>52</v>
+      </c>
       <c r="CY63" s="4"/>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
+      <c r="DB63" s="4"/>
     </row>
     <row r="64" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX64" s="4"/>
       <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
+      <c r="DB64" s="4"/>
     </row>
     <row r="65" spans="1:233" x14ac:dyDescent="0.2">
-      <c r="CX65" s="4"/>
       <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
+      <c r="DB65" s="4"/>
     </row>
     <row r="66" spans="1:233" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17"/>
@@ -9375,10 +9425,13 @@
       <c r="CU66" s="22"/>
       <c r="CV66" s="22"/>
       <c r="CW66" s="22"/>
-      <c r="CX66" s="23"/>
+      <c r="CX66" s="22" t="s">
+        <v>53</v>
+      </c>
       <c r="CY66" s="23"/>
       <c r="CZ66" s="23"/>
       <c r="DA66" s="23"/>
+      <c r="DB66" s="23"/>
     </row>
     <row r="67" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -9684,17 +9737,20 @@
       <c r="CW67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX67" s="24"/>
+      <c r="CX67" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY67" s="24"/>
       <c r="CZ67" s="24"/>
       <c r="DA67" s="24"/>
+      <c r="DB67" s="24"/>
     </row>
     <row r="68" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CX68" s="4"/>
       <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
+      <c r="DB68" s="4"/>
     </row>
     <row r="69" spans="1:233" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -10000,11 +10056,13 @@
       <c r="CW69" s="16">
         <v>4.0120354175971187</v>
       </c>
-      <c r="CX69" s="18"/>
+      <c r="CX69" s="16">
+        <v>2.4884688437385734</v>
+      </c>
       <c r="CY69" s="18"/>
       <c r="CZ69" s="18"/>
       <c r="DA69" s="18"/>
-      <c r="DB69" s="8"/>
+      <c r="DB69" s="18"/>
       <c r="DC69" s="8"/>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
@@ -10433,11 +10491,13 @@
       <c r="CW70" s="16">
         <v>6.6870197284988109</v>
       </c>
-      <c r="CX70" s="18"/>
+      <c r="CX70" s="16">
+        <v>4.6932058250123561</v>
+      </c>
       <c r="CY70" s="18"/>
       <c r="CZ70" s="18"/>
       <c r="DA70" s="18"/>
-      <c r="DB70" s="8"/>
+      <c r="DB70" s="18"/>
       <c r="DC70" s="8"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
@@ -10663,11 +10723,11 @@
       <c r="CU71" s="8"/>
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
-      <c r="CX71" s="7"/>
+      <c r="CX71" s="8"/>
       <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
-      <c r="DB71" s="8"/>
+      <c r="DB71" s="7"/>
       <c r="DC71" s="8"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
@@ -11096,11 +11156,13 @@
       <c r="CW72" s="16">
         <v>5.8150258549504343</v>
       </c>
-      <c r="CX72" s="18"/>
+      <c r="CX72" s="16">
+        <v>3.9887442034487037</v>
+      </c>
       <c r="CY72" s="18"/>
       <c r="CZ72" s="18"/>
       <c r="DA72" s="18"/>
-      <c r="DB72" s="8"/>
+      <c r="DB72" s="18"/>
       <c r="DC72" s="8"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
@@ -11327,19 +11389,20 @@
       <c r="CU73" s="10"/>
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
-      <c r="CX73" s="25"/>
+      <c r="CX73" s="10"/>
       <c r="CY73" s="25"/>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
+      <c r="DB73" s="25"/>
     </row>
     <row r="74" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX74" s="4"/>
       <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
+      <c r="DB74" s="4"/>
     </row>
     <row r="75" spans="1:233" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="8"/>
@@ -11446,7 +11509,7 @@
       <c r="CY75" s="7"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
-      <c r="DB75" s="8"/>
+      <c r="DB75" s="7"/>
       <c r="DC75" s="8"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
@@ -11680,7 +11743,7 @@
       <c r="CY76" s="7"/>
       <c r="CZ76" s="7"/>
       <c r="DA76" s="7"/>
-      <c r="DB76" s="8"/>
+      <c r="DB76" s="7"/>
       <c r="DC76" s="8"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
@@ -11817,21 +11880,24 @@
       <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
+      <c r="DB77" s="4"/>
     </row>
     <row r="78" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
+      <c r="DB78" s="4"/>
     </row>
     <row r="79" spans="1:233" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
       <c r="CY79" s="4"/>
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
+      <c r="DB79" s="4"/>
     </row>
     <row r="80" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -11841,10 +11907,11 @@
       <c r="CY80" s="4"/>
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
+      <c r="DB80" s="4"/>
     </row>
     <row r="81" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:233" x14ac:dyDescent="0.2">
@@ -12010,6 +12077,9 @@
       <c r="CY84" s="22"/>
       <c r="CZ84" s="22"/>
       <c r="DA84" s="22"/>
+      <c r="DB84" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="85" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -12326,6 +12396,9 @@
       </c>
       <c r="DA85" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB85" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12647,7 +12720,9 @@
       <c r="DA87" s="16">
         <v>121.02134109202511</v>
       </c>
-      <c r="DB87" s="8"/>
+      <c r="DB87" s="16">
+        <v>126.62407072470567</v>
+      </c>
       <c r="DC87" s="8"/>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
@@ -13092,7 +13167,9 @@
       <c r="DA88" s="16">
         <v>138.41961307760056</v>
       </c>
-      <c r="DB88" s="8"/>
+      <c r="DB88" s="16">
+        <v>151.67109426843791</v>
+      </c>
       <c r="DC88" s="8"/>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
@@ -13771,7 +13848,9 @@
       <c r="DA90" s="16">
         <v>132.84474540624905</v>
       </c>
-      <c r="DB90" s="8"/>
+      <c r="DB90" s="16">
+        <v>143.78348576320835</v>
+      </c>
       <c r="DC90" s="8"/>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
@@ -14006,6 +14085,7 @@
       <c r="CY91" s="10"/>
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
+      <c r="DB91" s="10"/>
     </row>
     <row r="92" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -14024,7 +14104,7 @@
     </row>
     <row r="97" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:233" x14ac:dyDescent="0.2">
@@ -14034,7 +14114,7 @@
     </row>
     <row r="100" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:233" x14ac:dyDescent="0.2">
@@ -14200,6 +14280,9 @@
       <c r="CY103" s="22"/>
       <c r="CZ103" s="22"/>
       <c r="DA103" s="22"/>
+      <c r="DB103" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="104" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -14516,6 +14599,9 @@
       </c>
       <c r="DA104" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB104" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14837,7 +14923,9 @@
       <c r="DA106" s="16">
         <v>29.190802038551332</v>
       </c>
-      <c r="DB106" s="8"/>
+      <c r="DB106" s="16">
+        <v>27.732976632272116</v>
+      </c>
       <c r="DC106" s="8"/>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
@@ -15282,7 +15370,9 @@
       <c r="DA107" s="16">
         <v>70.80919796144866</v>
       </c>
-      <c r="DB107" s="8"/>
+      <c r="DB107" s="16">
+        <v>72.267023367727873</v>
+      </c>
       <c r="DC107" s="8"/>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
@@ -15961,7 +16051,9 @@
       <c r="DA109" s="16">
         <v>100</v>
       </c>
-      <c r="DB109" s="8"/>
+      <c r="DB109" s="16">
+        <v>100</v>
+      </c>
       <c r="DC109" s="8"/>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
@@ -16196,6 +16288,7 @@
       <c r="CY110" s="10"/>
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
+      <c r="DB110" s="10"/>
     </row>
     <row r="111" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -16682,7 +16775,7 @@
     </row>
     <row r="116" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:233" x14ac:dyDescent="0.2">
@@ -16692,7 +16785,7 @@
     </row>
     <row r="119" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:233" x14ac:dyDescent="0.2">
@@ -16858,6 +16951,9 @@
       <c r="CY122" s="22"/>
       <c r="CZ122" s="22"/>
       <c r="DA122" s="22"/>
+      <c r="DB122" s="22">
+        <v>2026</v>
+      </c>
     </row>
     <row r="123" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -17174,6 +17270,9 @@
       </c>
       <c r="DA123" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB123" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17495,7 +17594,9 @@
       <c r="DA125" s="16">
         <v>32.042651568923183</v>
       </c>
-      <c r="DB125" s="8"/>
+      <c r="DB125" s="16">
+        <v>31.491200906398248</v>
+      </c>
       <c r="DC125" s="8"/>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
@@ -17940,7 +18041,9 @@
       <c r="DA126" s="16">
         <v>67.957348431076809</v>
       </c>
-      <c r="DB126" s="8"/>
+      <c r="DB126" s="16">
+        <v>68.508799093601752</v>
+      </c>
       <c r="DC126" s="8"/>
       <c r="DD126" s="8"/>
       <c r="DE126" s="8"/>
@@ -18619,7 +18722,9 @@
       <c r="DA128" s="16">
         <v>100</v>
       </c>
-      <c r="DB128" s="8"/>
+      <c r="DB128" s="16">
+        <v>100</v>
+      </c>
       <c r="DC128" s="8"/>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
@@ -18854,6 +18959,7 @@
       <c r="CY129" s="10"/>
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
+      <c r="DB129" s="10"/>
     </row>
     <row r="130" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -18966,7 +19072,7 @@
       <c r="CY131" s="14"/>
       <c r="CZ131" s="14"/>
       <c r="DA131" s="14"/>
-      <c r="DB131" s="13"/>
+      <c r="DB131" s="14"/>
       <c r="DC131" s="13"/>
       <c r="DD131" s="13"/>
       <c r="DE131" s="13"/>
@@ -19109,9 +19215,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="81" man="1"/>
-    <brk id="76" max="81" man="1"/>
-    <brk id="94" max="81" man="1"/>
+    <brk id="38" max="105" man="1"/>
+    <brk id="76" max="105" man="1"/>
+    <brk id="94" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-15AFSA_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614E9163-9017-4D01-9899-D8EDB4BB8E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D9D523-4F4E-4D5D-AAAF-4A466850E59E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">AFSA!$A$1:$DB$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">AFSA!$A$1:$DC$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,13 +685,13 @@
     <t>Table 16.7 Gross Value Added in Accommodation and Food Service Activities, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1195,8 +1195,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.7109375" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="3" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="3"/>
+    <col min="2" max="107" width="13" style="3" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:233" x14ac:dyDescent="0.2">
@@ -1211,7 +1211,7 @@
     </row>
     <row r="3" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:233" x14ac:dyDescent="0.2">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="6" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:233" x14ac:dyDescent="0.2">
@@ -1390,6 +1390,7 @@
       <c r="DB9" s="22">
         <v>2026</v>
       </c>
+      <c r="DC9" s="22"/>
     </row>
     <row r="10" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1709,6 +1710,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2031,9 +2035,11 @@
         <v>52197.206566962675</v>
       </c>
       <c r="DB12" s="19">
-        <v>53445.042458122043</v>
-      </c>
-      <c r="DC12" s="8"/>
+        <v>54028.593926819856</v>
+      </c>
+      <c r="DC12" s="19">
+        <v>39915.258435718606</v>
+      </c>
       <c r="DD12" s="8"/>
       <c r="DE12" s="8"/>
       <c r="DF12" s="8"/>
@@ -2478,9 +2484,11 @@
         <v>126616.67630623671</v>
       </c>
       <c r="DB13" s="19">
-        <v>139267.9258134824</v>
-      </c>
-      <c r="DC13" s="8"/>
+        <v>140080.49290314427</v>
+      </c>
+      <c r="DC13" s="19">
+        <v>106788.74002951186</v>
+      </c>
       <c r="DD13" s="8"/>
       <c r="DE13" s="8"/>
       <c r="DF13" s="8"/>
@@ -3159,9 +3167,11 @@
         <v>178813.88287319939</v>
       </c>
       <c r="DB15" s="20">
-        <v>192712.96827160445</v>
-      </c>
-      <c r="DC15" s="8"/>
+        <v>194109.08682996413</v>
+      </c>
+      <c r="DC15" s="20">
+        <v>146703.99846523046</v>
+      </c>
       <c r="DD15" s="8"/>
       <c r="DE15" s="8"/>
       <c r="DF15" s="8"/>
@@ -3396,6 +3406,7 @@
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
       <c r="DB16" s="10"/>
+      <c r="DC16" s="10"/>
     </row>
     <row r="17" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3742,7 +3753,7 @@
       <c r="CZ19" s="21"/>
       <c r="DA19" s="21"/>
       <c r="DB19" s="21"/>
-      <c r="DC19" s="8"/>
+      <c r="DC19" s="21"/>
       <c r="DD19" s="8"/>
       <c r="DE19" s="8"/>
       <c r="DF19" s="8"/>
@@ -3882,7 +3893,7 @@
     </row>
     <row r="22" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:233" x14ac:dyDescent="0.2">
@@ -3892,7 +3903,7 @@
     </row>
     <row r="25" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:233" x14ac:dyDescent="0.2">
@@ -4061,6 +4072,7 @@
       <c r="DB28" s="22">
         <v>2026</v>
       </c>
+      <c r="DC28" s="22"/>
     </row>
     <row r="29" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4380,6 +4392,9 @@
       </c>
       <c r="DB29" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC29" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4702,9 +4717,11 @@
         <v>43130.580190209352</v>
       </c>
       <c r="DB31" s="19">
-        <v>42207.64831855493</v>
-      </c>
-      <c r="DC31" s="8"/>
+        <v>42668.50182402035</v>
+      </c>
+      <c r="DC31" s="19">
+        <v>31695.297145792541</v>
+      </c>
       <c r="DD31" s="8"/>
       <c r="DE31" s="8"/>
       <c r="DF31" s="8"/>
@@ -5149,9 +5166,11 @@
         <v>91473.074870721612</v>
       </c>
       <c r="DB32" s="19">
-        <v>91822.325463675021</v>
-      </c>
-      <c r="DC32" s="8"/>
+        <v>92364.303959092911</v>
+      </c>
+      <c r="DC32" s="19">
+        <v>71845.417645077934</v>
+      </c>
       <c r="DD32" s="8"/>
       <c r="DE32" s="8"/>
       <c r="DF32" s="8"/>
@@ -5830,9 +5849,11 @@
         <v>134603.65506093096</v>
       </c>
       <c r="DB34" s="20">
-        <v>134029.97378222994</v>
-      </c>
-      <c r="DC34" s="8"/>
+        <v>135032.80578311326</v>
+      </c>
+      <c r="DC34" s="20">
+        <v>103540.71479087048</v>
+      </c>
       <c r="DD34" s="8"/>
       <c r="DE34" s="8"/>
       <c r="DF34" s="8"/>
@@ -6067,6 +6088,7 @@
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
       <c r="DB35" s="10"/>
+      <c r="DC35" s="10"/>
     </row>
     <row r="36" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6179,7 +6201,7 @@
       <c r="CZ37" s="7"/>
       <c r="DA37" s="7"/>
       <c r="DB37" s="7"/>
-      <c r="DC37" s="8"/>
+      <c r="DC37" s="7"/>
       <c r="DD37" s="8"/>
       <c r="DE37" s="8"/>
       <c r="DF37" s="8"/>
@@ -6413,7 +6435,7 @@
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
       <c r="DB38" s="7"/>
-      <c r="DC38" s="8"/>
+      <c r="DC38" s="7"/>
       <c r="DD38" s="8"/>
       <c r="DE38" s="8"/>
       <c r="DF38" s="8"/>
@@ -6550,6 +6572,7 @@
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
       <c r="DB39" s="4"/>
+      <c r="DC39" s="4"/>
     </row>
     <row r="40" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -6560,16 +6583,18 @@
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
       <c r="DB40" s="4"/>
+      <c r="DC40" s="4"/>
     </row>
     <row r="41" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
       <c r="DB41" s="4"/>
+      <c r="DC41" s="4"/>
     </row>
     <row r="42" spans="1:233" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
@@ -6577,6 +6602,7 @@
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
       <c r="DB42" s="4"/>
+      <c r="DC42" s="4"/>
     </row>
     <row r="43" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -6587,16 +6613,18 @@
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
       <c r="DB43" s="4"/>
+      <c r="DC43" s="4"/>
     </row>
     <row r="44" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX44" s="4"/>
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
       <c r="DB44" s="4"/>
+      <c r="DC44" s="4"/>
     </row>
     <row r="45" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6607,13 +6635,13 @@
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
       <c r="DB45" s="4"/>
+      <c r="DC45" s="4"/>
     </row>
     <row r="46" spans="1:233" x14ac:dyDescent="0.2">
-      <c r="CX46" s="4"/>
-      <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
       <c r="DB46" s="4"/>
+      <c r="DC46" s="4"/>
     </row>
     <row r="47" spans="1:233" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
@@ -6768,12 +6796,13 @@
       <c r="CV47" s="22"/>
       <c r="CW47" s="22"/>
       <c r="CX47" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY47" s="23"/>
+        <v>51</v>
+      </c>
+      <c r="CY47" s="22"/>
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
       <c r="DB47" s="23"/>
+      <c r="DC47" s="23"/>
     </row>
     <row r="48" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -7082,17 +7111,20 @@
       <c r="CX48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY48" s="24"/>
+      <c r="CY48" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ48" s="24"/>
       <c r="DA48" s="24"/>
       <c r="DB48" s="24"/>
+      <c r="DC48" s="24"/>
     </row>
     <row r="49" spans="1:229" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
       <c r="DB49" s="4"/>
+      <c r="DC49" s="4"/>
     </row>
     <row r="50" spans="1:229" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -7399,13 +7431,15 @@
         <v>6.3430507125864892</v>
       </c>
       <c r="CX50" s="16">
-        <v>5.4057049241340565</v>
-      </c>
-      <c r="CY50" s="18"/>
+        <v>6.5566003316136943</v>
+      </c>
+      <c r="CY50" s="16">
+        <v>6.8868560348323626</v>
+      </c>
       <c r="CZ50" s="18"/>
       <c r="DA50" s="18"/>
       <c r="DB50" s="18"/>
-      <c r="DC50" s="8"/>
+      <c r="DC50" s="18"/>
       <c r="DD50" s="8"/>
       <c r="DE50" s="8"/>
       <c r="DF50" s="8"/>
@@ -7834,13 +7868,15 @@
         <v>9.4091885308496614</v>
       </c>
       <c r="CX51" s="16">
-        <v>9.3777650219893474</v>
-      </c>
-      <c r="CY51" s="18"/>
+        <v>10.015936170719357</v>
+      </c>
+      <c r="CY51" s="16">
+        <v>7.7566591307856925</v>
+      </c>
       <c r="CZ51" s="18"/>
       <c r="DA51" s="18"/>
       <c r="DB51" s="18"/>
-      <c r="DC51" s="8"/>
+      <c r="DC51" s="18"/>
       <c r="DD51" s="8"/>
       <c r="DE51" s="8"/>
       <c r="DF51" s="8"/>
@@ -8067,11 +8103,11 @@
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
       <c r="CX52" s="8"/>
-      <c r="CY52" s="7"/>
+      <c r="CY52" s="8"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
       <c r="DB52" s="7"/>
-      <c r="DC52" s="8"/>
+      <c r="DC52" s="7"/>
       <c r="DD52" s="8"/>
       <c r="DE52" s="8"/>
       <c r="DF52" s="8"/>
@@ -8500,13 +8536,15 @@
         <v>8.4960378169290465</v>
       </c>
       <c r="CX53" s="16">
-        <v>8.2465059724088547</v>
-      </c>
-      <c r="CY53" s="18"/>
+        <v>9.0307030984303935</v>
+      </c>
+      <c r="CY53" s="16">
+        <v>7.5186041577388636</v>
+      </c>
       <c r="CZ53" s="18"/>
       <c r="DA53" s="18"/>
       <c r="DB53" s="18"/>
-      <c r="DC53" s="8"/>
+      <c r="DC53" s="18"/>
       <c r="DD53" s="8"/>
       <c r="DE53" s="8"/>
       <c r="DF53" s="8"/>
@@ -8733,19 +8771,20 @@
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
       <c r="CX54" s="10"/>
-      <c r="CY54" s="25"/>
+      <c r="CY54" s="10"/>
       <c r="CZ54" s="25"/>
       <c r="DA54" s="25"/>
       <c r="DB54" s="25"/>
+      <c r="DC54" s="25"/>
     </row>
     <row r="55" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
       <c r="DB55" s="4"/>
+      <c r="DC55" s="4"/>
     </row>
     <row r="56" spans="1:229" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -8849,11 +8888,11 @@
       <c r="CV56" s="8"/>
       <c r="CW56" s="8"/>
       <c r="CX56" s="8"/>
-      <c r="CY56" s="7"/>
+      <c r="CY56" s="8"/>
       <c r="CZ56" s="7"/>
       <c r="DA56" s="7"/>
       <c r="DB56" s="7"/>
-      <c r="DC56" s="8"/>
+      <c r="DC56" s="7"/>
       <c r="DD56" s="8"/>
       <c r="DE56" s="8"/>
       <c r="DF56" s="8"/>
@@ -9079,11 +9118,11 @@
       <c r="CV57" s="8"/>
       <c r="CW57" s="8"/>
       <c r="CX57" s="8"/>
-      <c r="CY57" s="7"/>
+      <c r="CY57" s="8"/>
       <c r="CZ57" s="7"/>
       <c r="DA57" s="7"/>
       <c r="DB57" s="7"/>
-      <c r="DC57" s="8"/>
+      <c r="DC57" s="7"/>
       <c r="DD57" s="8"/>
       <c r="DE57" s="8"/>
       <c r="DF57" s="8"/>
@@ -9211,67 +9250,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
       <c r="DB58" s="4"/>
+      <c r="DC58" s="4"/>
     </row>
     <row r="59" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
       <c r="DB59" s="4"/>
+      <c r="DC59" s="4"/>
     </row>
     <row r="60" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="CY60" s="4"/>
+        <v>52</v>
+      </c>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
       <c r="DB60" s="4"/>
+      <c r="DC60" s="4"/>
     </row>
     <row r="61" spans="1:229" x14ac:dyDescent="0.2">
-      <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
       <c r="DB61" s="4"/>
+      <c r="DC61" s="4"/>
     </row>
     <row r="62" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
       <c r="DB62" s="4"/>
+      <c r="DC62" s="4"/>
     </row>
     <row r="63" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CY63" s="4"/>
+        <v>53</v>
+      </c>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
       <c r="DB63" s="4"/>
+      <c r="DC63" s="4"/>
     </row>
     <row r="64" spans="1:229" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
       <c r="DB64" s="4"/>
+      <c r="DC64" s="4"/>
     </row>
     <row r="65" spans="1:233" x14ac:dyDescent="0.2">
-      <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
       <c r="DB65" s="4"/>
+      <c r="DC65" s="4"/>
     </row>
     <row r="66" spans="1:233" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17"/>
@@ -9426,12 +9465,13 @@
       <c r="CV66" s="22"/>
       <c r="CW66" s="22"/>
       <c r="CX66" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="23"/>
+        <v>51</v>
+      </c>
+      <c r="CY66" s="22"/>
       <c r="CZ66" s="23"/>
       <c r="DA66" s="23"/>
       <c r="DB66" s="23"/>
+      <c r="DC66" s="23"/>
     </row>
     <row r="67" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -9740,17 +9780,20 @@
       <c r="CX67" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY67" s="24"/>
+      <c r="CY67" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ67" s="24"/>
       <c r="DA67" s="24"/>
       <c r="DB67" s="24"/>
+      <c r="DC67" s="24"/>
     </row>
     <row r="68" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
       <c r="DB68" s="4"/>
+      <c r="DC68" s="4"/>
     </row>
     <row r="69" spans="1:233" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -10057,13 +10100,15 @@
         <v>4.0120354175971187</v>
       </c>
       <c r="CX69" s="16">
-        <v>2.4884688437385734</v>
-      </c>
-      <c r="CY69" s="18"/>
+        <v>3.6075117664795755</v>
+      </c>
+      <c r="CY69" s="16">
+        <v>3.0554735437784188</v>
+      </c>
       <c r="CZ69" s="18"/>
       <c r="DA69" s="18"/>
       <c r="DB69" s="18"/>
-      <c r="DC69" s="8"/>
+      <c r="DC69" s="18"/>
       <c r="DD69" s="8"/>
       <c r="DE69" s="8"/>
       <c r="DF69" s="8"/>
@@ -10492,13 +10537,15 @@
         <v>6.6870197284988109</v>
       </c>
       <c r="CX70" s="16">
-        <v>4.6932058250123561</v>
-      </c>
-      <c r="CY70" s="18"/>
+        <v>5.3111543019975329</v>
+      </c>
+      <c r="CY70" s="16">
+        <v>1.0539689417639977</v>
+      </c>
       <c r="CZ70" s="18"/>
       <c r="DA70" s="18"/>
       <c r="DB70" s="18"/>
-      <c r="DC70" s="8"/>
+      <c r="DC70" s="18"/>
       <c r="DD70" s="8"/>
       <c r="DE70" s="8"/>
       <c r="DF70" s="8"/>
@@ -10724,11 +10771,11 @@
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
       <c r="CX71" s="8"/>
-      <c r="CY71" s="7"/>
+      <c r="CY71" s="8"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
       <c r="DB71" s="7"/>
-      <c r="DC71" s="8"/>
+      <c r="DC71" s="7"/>
       <c r="DD71" s="8"/>
       <c r="DE71" s="8"/>
       <c r="DF71" s="8"/>
@@ -11157,13 +11204,15 @@
         <v>5.8150258549504343</v>
       </c>
       <c r="CX72" s="16">
-        <v>3.9887442034487037</v>
-      </c>
-      <c r="CY72" s="18"/>
+        <v>4.7668033007990402</v>
+      </c>
+      <c r="CY72" s="16">
+        <v>1.6583519744324491</v>
+      </c>
       <c r="CZ72" s="18"/>
       <c r="DA72" s="18"/>
       <c r="DB72" s="18"/>
-      <c r="DC72" s="8"/>
+      <c r="DC72" s="18"/>
       <c r="DD72" s="8"/>
       <c r="DE72" s="8"/>
       <c r="DF72" s="8"/>
@@ -11390,19 +11439,20 @@
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
       <c r="CX73" s="10"/>
-      <c r="CY73" s="25"/>
+      <c r="CY73" s="10"/>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
       <c r="DB73" s="25"/>
+      <c r="DC73" s="25"/>
     </row>
     <row r="74" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
       <c r="DB74" s="4"/>
+      <c r="DC74" s="4"/>
     </row>
     <row r="75" spans="1:233" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="8"/>
@@ -11505,12 +11555,12 @@
       <c r="CU75" s="8"/>
       <c r="CV75" s="8"/>
       <c r="CW75" s="8"/>
-      <c r="CX75" s="7"/>
-      <c r="CY75" s="7"/>
+      <c r="CX75" s="8"/>
+      <c r="CY75" s="8"/>
       <c r="CZ75" s="7"/>
       <c r="DA75" s="7"/>
       <c r="DB75" s="7"/>
-      <c r="DC75" s="8"/>
+      <c r="DC75" s="7"/>
       <c r="DD75" s="8"/>
       <c r="DE75" s="8"/>
       <c r="DF75" s="8"/>
@@ -11739,12 +11789,12 @@
       <c r="CU76" s="8"/>
       <c r="CV76" s="8"/>
       <c r="CW76" s="8"/>
-      <c r="CX76" s="7"/>
+      <c r="CX76" s="8"/>
       <c r="CY76" s="7"/>
       <c r="CZ76" s="7"/>
       <c r="DA76" s="7"/>
       <c r="DB76" s="7"/>
-      <c r="DC76" s="8"/>
+      <c r="DC76" s="7"/>
       <c r="DD76" s="8"/>
       <c r="DE76" s="8"/>
       <c r="DF76" s="8"/>
@@ -11881,16 +11931,18 @@
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
       <c r="DB77" s="4"/>
+      <c r="DC77" s="4"/>
     </row>
     <row r="78" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
       <c r="DB78" s="4"/>
+      <c r="DC78" s="4"/>
     </row>
     <row r="79" spans="1:233" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
@@ -11898,6 +11950,7 @@
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
       <c r="DB79" s="4"/>
+      <c r="DC79" s="4"/>
     </row>
     <row r="80" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -11908,10 +11961,11 @@
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
       <c r="DB80" s="4"/>
+      <c r="DC80" s="4"/>
     </row>
     <row r="81" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:233" x14ac:dyDescent="0.2">
@@ -12080,6 +12134,7 @@
       <c r="DB84" s="22">
         <v>2026</v>
       </c>
+      <c r="DC84" s="22"/>
     </row>
     <row r="85" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -12399,6 +12454,9 @@
       </c>
       <c r="DB85" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC85" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -12723,7 +12781,9 @@
       <c r="DB87" s="16">
         <v>126.62407072470567</v>
       </c>
-      <c r="DC87" s="8"/>
+      <c r="DC87" s="16">
+        <v>125.93432474261323</v>
+      </c>
       <c r="DD87" s="8"/>
       <c r="DE87" s="8"/>
       <c r="DF87" s="8"/>
@@ -13168,9 +13228,11 @@
         <v>138.41961307760056</v>
       </c>
       <c r="DB88" s="16">
-        <v>151.67109426843791</v>
-      </c>
-      <c r="DC88" s="8"/>
+        <v>151.66085478778069</v>
+      </c>
+      <c r="DC88" s="16">
+        <v>148.6368143296998</v>
+      </c>
       <c r="DD88" s="8"/>
       <c r="DE88" s="8"/>
       <c r="DF88" s="8"/>
@@ -13849,9 +13911,11 @@
         <v>132.84474540624905</v>
       </c>
       <c r="DB90" s="16">
-        <v>143.78348576320835</v>
-      </c>
-      <c r="DC90" s="8"/>
+        <v>143.74957678191024</v>
+      </c>
+      <c r="DC90" s="16">
+        <v>141.68725680669709</v>
+      </c>
       <c r="DD90" s="8"/>
       <c r="DE90" s="8"/>
       <c r="DF90" s="8"/>
@@ -14086,6 +14150,7 @@
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
       <c r="DB91" s="10"/>
+      <c r="DC91" s="10"/>
     </row>
     <row r="92" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -14104,7 +14169,7 @@
     </row>
     <row r="97" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:233" x14ac:dyDescent="0.2">
@@ -14114,7 +14179,7 @@
     </row>
     <row r="100" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:233" x14ac:dyDescent="0.2">
@@ -14283,6 +14348,7 @@
       <c r="DB103" s="22">
         <v>2026</v>
       </c>
+      <c r="DC103" s="22"/>
     </row>
     <row r="104" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -14602,6 +14668,9 @@
       </c>
       <c r="DB104" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC104" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -14924,9 +14993,11 @@
         <v>29.190802038551332</v>
       </c>
       <c r="DB106" s="16">
-        <v>27.732976632272116</v>
-      </c>
-      <c r="DC106" s="8"/>
+        <v>27.834139456927058</v>
+      </c>
+      <c r="DC106" s="16">
+        <v>27.208023539439324</v>
+      </c>
       <c r="DD106" s="8"/>
       <c r="DE106" s="8"/>
       <c r="DF106" s="8"/>
@@ -15371,9 +15442,11 @@
         <v>70.80919796144866</v>
       </c>
       <c r="DB107" s="16">
-        <v>72.267023367727873</v>
-      </c>
-      <c r="DC107" s="8"/>
+        <v>72.165860543072938</v>
+      </c>
+      <c r="DC107" s="16">
+        <v>72.791976460560676</v>
+      </c>
       <c r="DD107" s="8"/>
       <c r="DE107" s="8"/>
       <c r="DF107" s="8"/>
@@ -16054,7 +16127,9 @@
       <c r="DB109" s="16">
         <v>100</v>
       </c>
-      <c r="DC109" s="8"/>
+      <c r="DC109" s="16">
+        <v>100</v>
+      </c>
       <c r="DD109" s="8"/>
       <c r="DE109" s="8"/>
       <c r="DF109" s="8"/>
@@ -16289,6 +16364,7 @@
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
       <c r="DB110" s="10"/>
+      <c r="DC110" s="10"/>
     </row>
     <row r="111" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -16775,7 +16851,7 @@
     </row>
     <row r="116" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:233" x14ac:dyDescent="0.2">
@@ -16785,7 +16861,7 @@
     </row>
     <row r="119" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:233" x14ac:dyDescent="0.2">
@@ -16954,6 +17030,7 @@
       <c r="DB122" s="22">
         <v>2026</v>
       </c>
+      <c r="DC122" s="22"/>
     </row>
     <row r="123" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -17273,6 +17350,9 @@
       </c>
       <c r="DB123" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC123" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:233" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17595,9 +17675,11 @@
         <v>32.042651568923183</v>
       </c>
       <c r="DB125" s="16">
-        <v>31.491200906398248</v>
-      </c>
-      <c r="DC125" s="8"/>
+        <v>31.59861899970705</v>
+      </c>
+      <c r="DC125" s="16">
+        <v>30.611433589009007</v>
+      </c>
       <c r="DD125" s="8"/>
       <c r="DE125" s="8"/>
       <c r="DF125" s="8"/>
@@ -18042,9 +18124,11 @@
         <v>67.957348431076809</v>
       </c>
       <c r="DB126" s="16">
-        <v>68.508799093601752</v>
-      </c>
-      <c r="DC126" s="8"/>
+        <v>68.401381000292943</v>
+      </c>
+      <c r="DC126" s="16">
+        <v>69.38856641099099</v>
+      </c>
       <c r="DD126" s="8"/>
       <c r="DE126" s="8"/>
       <c r="DF126" s="8"/>
@@ -18725,7 +18809,9 @@
       <c r="DB128" s="16">
         <v>100</v>
       </c>
-      <c r="DC128" s="8"/>
+      <c r="DC128" s="16">
+        <v>100</v>
+      </c>
       <c r="DD128" s="8"/>
       <c r="DE128" s="8"/>
       <c r="DF128" s="8"/>
@@ -18960,6 +19046,7 @@
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
       <c r="DB129" s="10"/>
+      <c r="DC129" s="10"/>
     </row>
     <row r="130" spans="1:233" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -19073,7 +19160,7 @@
       <c r="CZ131" s="14"/>
       <c r="DA131" s="14"/>
       <c r="DB131" s="14"/>
-      <c r="DC131" s="13"/>
+      <c r="DC131" s="14"/>
       <c r="DD131" s="13"/>
       <c r="DE131" s="13"/>
       <c r="DF131" s="13"/>
@@ -19208,6 +19295,8 @@
       <c r="CY132" s="6"/>
       <c r="CZ132" s="6"/>
       <c r="DA132" s="6"/>
+      <c r="DB132" s="6"/>
+      <c r="DC132" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -19215,9 +19304,9 @@
   <pageSetup paperSize="9" scale="48" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="105" man="1"/>
-    <brk id="76" max="105" man="1"/>
-    <brk id="94" max="105" man="1"/>
+    <brk id="38" max="106" man="1"/>
+    <brk id="76" max="106" man="1"/>
+    <brk id="94" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>